--- a/data/weeks/SSS_PS_17.09.2026-23.09.2026.xlsx
+++ b/data/weeks/SSS_PS_17.09.2026-23.09.2026.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Score (Avg Raw Value)</t>
+          <t>Score</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
